--- a/code_mapping/[공통] 3. 부서코드매핑정의서.xlsx
+++ b/code_mapping/[공통] 3. 부서코드매핑정의서.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <t>부서코드매핑정의서</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -157,6 +157,14 @@
   </si>
   <si>
     <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부서코드매핑정의서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260513</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -572,7 +580,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -588,27 +596,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -618,9 +611,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -639,9 +629,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -654,9 +641,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -672,6 +656,162 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -688,18 +828,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -999,205 +1127,223 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G21"/>
+  <dimension ref="B1:G22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.125" customWidth="1"/>
-    <col min="2" max="7" width="30.625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="2.125" style="62" customWidth="1"/>
+    <col min="2" max="3" width="30.625" style="53" customWidth="1"/>
+    <col min="4" max="4" width="30.625" style="54" customWidth="1"/>
+    <col min="5" max="6" width="30.625" style="53" customWidth="1"/>
+    <col min="7" max="7" width="30.625" style="54" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="62"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="33" t="s">
+    <row r="1" spans="2:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" s="63" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="30"/>
+    </row>
+    <row r="3" spans="2:7" s="63" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="35"/>
-    </row>
-    <row r="3" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="36"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="38"/>
-    </row>
-    <row r="4" spans="2:7" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="29" t="s">
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="66"/>
+    </row>
+    <row r="4" spans="2:7" s="63" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="67"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="69"/>
+    </row>
+    <row r="5" spans="2:7" s="63" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="32"/>
+    </row>
+    <row r="6" spans="2:7" s="63" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C6" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D6" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E6" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F6" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G6" s="34" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="16" t="s">
+    <row r="7" spans="2:7" s="63" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C7" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D7" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E7" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F7" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G7" s="40" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="13"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="15"/>
-    </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="2"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="11"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="44"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="5"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="9"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="48"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="5"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="9"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="48"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="5"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="9"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="48"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="5"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="9"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="48"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="5"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="9"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="48"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="5"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="9"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="48"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="5"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="9"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="48"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="5"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="9"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="48"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B17" s="5"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="9"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="48"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="5"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="9"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="48"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B19" s="5"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="9"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="48"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="5"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="9"/>
-    </row>
-    <row r="21" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="7"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="10"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="48"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="45"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="48"/>
+    </row>
+    <row r="22" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="49"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="52"/>
     </row>
   </sheetData>
+  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="1">
-    <mergeCell ref="B2:G3"/>
+    <mergeCell ref="B3:G4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1212,95 +1358,95 @@
   <cols>
     <col min="1" max="1" width="2.125" customWidth="1"/>
     <col min="2" max="6" width="30.625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="30.625" style="32" customWidth="1"/>
+    <col min="7" max="7" width="30.625" style="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="35"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="72"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="36"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="38"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="75"/>
     </row>
     <row r="4" spans="2:7" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="39"/>
+      <c r="G4" s="25"/>
     </row>
     <row r="5" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="23" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="13">
+      <c r="B7" s="8">
         <v>1000000</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="9">
         <v>1000</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="9">
         <v>1000</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="40" t="s">
+      <c r="G7" s="26" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1308,7 +1454,7 @@
       <c r="B8" s="2">
         <v>2000000</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="19" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="1">
@@ -1317,10 +1463,10 @@
       <c r="E8" s="1">
         <v>2000</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="G8" s="27" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1328,7 +1474,7 @@
       <c r="B9" s="2">
         <v>3000000</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="19" t="s">
         <v>29</v>
       </c>
       <c r="D9" s="1">
@@ -1337,10 +1483,10 @@
       <c r="E9" s="1">
         <v>3000</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="G9" s="27" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1348,7 +1494,7 @@
       <c r="B10" s="2">
         <v>4000000</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="19" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="1">
@@ -1357,104 +1503,105 @@
       <c r="E10" s="1">
         <v>4000</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="41" t="s">
+      <c r="G10" s="27" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
-      <c r="C11" s="26"/>
+      <c r="C11" s="19"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="41" t="s">
+      <c r="F11" s="15"/>
+      <c r="G11" s="27" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
-      <c r="C12" s="26"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="41"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="27"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
-      <c r="C13" s="26"/>
+      <c r="C13" s="19"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="41"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="27"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
-      <c r="C14" s="26"/>
+      <c r="C14" s="19"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="41"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="27"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
-      <c r="C15" s="26"/>
+      <c r="C15" s="19"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="41"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="27"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="2"/>
-      <c r="C16" s="26"/>
+      <c r="C16" s="19"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="41"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="27"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="2"/>
-      <c r="C17" s="26"/>
+      <c r="C17" s="19"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="41"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="27"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="2"/>
-      <c r="C18" s="26"/>
+      <c r="C18" s="19"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="41"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="27"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="2"/>
-      <c r="C19" s="26"/>
+      <c r="C19" s="19"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="41"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="27"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="2"/>
-      <c r="C20" s="26"/>
+      <c r="C20" s="19"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="41"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="27"/>
     </row>
     <row r="21" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="7"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="42"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="28"/>
     </row>
   </sheetData>
+  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="B2:G3"/>
   </mergeCells>

--- a/code_mapping/[공통] 3. 부서코드매핑정의서.xlsx
+++ b/code_mapping/[공통] 3. 부서코드매핑정의서.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qkang\OneDrive\바탕 화면\migraion\01. 템플릿\통합\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="부서코드매핑정의서" sheetId="7" r:id="rId1"/>
@@ -164,7 +164,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20260513</t>
+    <t>20260903</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1341,7 +1341,7 @@
       <c r="G22" s="52"/>
     </row>
   </sheetData>
-  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Rt/BQ11qB325QZXThiAWraXtzyq9NvKesCSQCancl3JQEvIR8vrQeWtAiqwxlhpZOqNPXApq2wOxkWAjSP89qQ==" saltValue="UGLFZQy290MMAL2qI+nEkg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="B3:G4"/>
   </mergeCells>
@@ -1601,7 +1601,7 @@
       <c r="G21" s="28"/>
     </row>
   </sheetData>
-  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="iTTfaUH22hflksR1QIuY9IplWuOhq7vAM+m/TBSQ2vy4s03uNKogxftvRYwDqShPv961r/mxbnMuC2pyhWkxyQ==" saltValue="758pE8dls6EmeFOnapnNRA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="B2:G3"/>
   </mergeCells>
